--- a/archivos_varios/Excel para SCORE2/SCORE2_PruebaFinal.xlsx
+++ b/archivos_varios/Excel para SCORE2/SCORE2_PruebaFinal.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Hernán\Desktop\Administracion HernanMayol\Python_ISSUNNE\Archivos varios\Excel para SCORE2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Hernán\Desktop\Administracion HernanMayol\Python_ISSUNNE\archivos_varios\Excel para SCORE2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6B504D1-506C-4F21-AF45-BB6B361C1BDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61130BD3-85DD-4BE2-80BE-09E19B811BE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10245" windowHeight="11070" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pacientes" sheetId="1" r:id="rId1"/>
@@ -122,12 +122,6 @@
     <t>P004</t>
   </si>
   <si>
-    <t>BAJO</t>
-  </si>
-  <si>
-    <t>ALTO</t>
-  </si>
-  <si>
     <t>MODERADO</t>
   </si>
   <si>
@@ -231,6 +225,12 @@
   </si>
   <si>
     <t>P008</t>
+  </si>
+  <si>
+    <t>MUY ALTO</t>
+  </si>
+  <si>
+    <t>Riesgo Bajo-moderado</t>
   </si>
 </sst>
 </file>
@@ -699,7 +699,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1010,7 +1010,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>80</c:v>
+                  <c:v>81</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>58</c:v>
@@ -1034,7 +1034,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>7.75</c:v>
+                  <c:v>7.2899999999999991</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>8.36</c:v>
@@ -3875,13 +3875,12 @@
     <col min="5" max="5" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -3917,7 +3916,7 @@
         <v>5</v>
       </c>
       <c r="H3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I3" t="s">
         <v>6</v>
@@ -3928,7 +3927,7 @@
         <v>23</v>
       </c>
       <c r="B4">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
@@ -3937,13 +3936,13 @@
         <v>8</v>
       </c>
       <c r="E4">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="F4">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="G4">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="I4" t="s">
         <v>27</v>
@@ -3972,7 +3971,7 @@
         <v>48</v>
       </c>
       <c r="I5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -3998,7 +3997,7 @@
         <v>40</v>
       </c>
       <c r="I6" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -4029,7 +4028,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B8">
         <v>55</v>
@@ -4050,12 +4049,12 @@
         <v>40</v>
       </c>
       <c r="I8" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B9">
         <v>55</v>
@@ -4081,7 +4080,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B10" s="1">
         <v>60</v>
@@ -4102,12 +4101,12 @@
         <v>40</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B11" s="1">
         <v>45</v>
@@ -4129,7 +4128,7 @@
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -4149,7 +4148,7 @@
     <row r="18" spans="1:5" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -4192,16 +4191,16 @@
         <v>17</v>
       </c>
       <c r="D1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" t="s">
         <v>55</v>
       </c>
-      <c r="E1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F1" t="s">
-        <v>57</v>
-      </c>
       <c r="G1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H1" t="s">
         <v>18</v>
@@ -4217,11 +4216,11 @@
       </c>
       <c r="B2">
         <f>Pacientes!F4/38.67</f>
-        <v>4.6547711404189291</v>
+        <v>4.189294026377036</v>
       </c>
       <c r="C2">
         <f xml:space="preserve"> Pacientes!G4/38.67</f>
-        <v>1.4222911817946728</v>
+        <v>1.1895526247737263</v>
       </c>
       <c r="D2">
         <f>IF(Pacientes!B4&lt;45,40,
@@ -4244,7 +4243,7 @@
         <f>IF(Pacientes!F4&lt;145,130,
  IF(Pacientes!F4&lt;175,160,
  IF(Pacientes!F4&lt;205,190,220)))</f>
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="G2" t="str">
         <f>IF(Pacientes!B4&gt;=70,"SCORE2-OP","SCORE2")</f>
@@ -4255,7 +4254,7 @@
     IF(OR(Pacientes!D4="Si", Pacientes!D4="Sí"), (0.14*Pacientes!B4 + 0.08*Pacientes!E4 + 0.04*(Pacientes!F4-Pacientes!G4)-16), (0.11*Pacientes!B4 + 0.06*Pacientes!E4 + 0.03*(Pacientes!F4-Pacientes!G4)-12)),
     IF(OR(Pacientes!D4="Si", Pacientes!D4="Sí"), (0.1*Pacientes!B4 + 0.06*Pacientes!E4 + 0.03*(Pacientes!F4-Pacientes!G4)-11), (0.08*Pacientes!B4 + 0.05*Pacientes!E4 + 0.02*(Pacientes!F4-Pacientes!G4)-9))
 )</f>
-        <v>7.75</v>
+        <v>7.2899999999999991</v>
       </c>
       <c r="I2" s="6" t="str">
         <f t="shared" ref="I2:I8" si="0">IF(G2="SCORE2",
@@ -4268,7 +4267,7 @@
              "Riesgo Muy Alto")),
        "")
 )</f>
-        <v>Riesgo Alto</v>
+        <v>Riesgo Bajo-Moderado</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -4678,33 +4677,33 @@
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>57</v>
-      </c>
       <c r="F1" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C2" s="8">
         <v>55</v>
@@ -4724,10 +4723,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C3" s="8">
         <v>55</v>
@@ -4739,7 +4738,7 @@
         <v>160</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G3" s="8">
         <v>6.2</v>
@@ -4747,10 +4746,10 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C4" s="8">
         <v>55</v>
@@ -4770,10 +4769,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C5">
         <v>80</v>
@@ -4785,7 +4784,7 @@
         <v>190</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G5">
         <v>7.75</v>
@@ -4818,22 +4817,22 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
       </c>
       <c r="E1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G1" t="s">
         <v>2</v>
       </c>
       <c r="H1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -4846,11 +4845,11 @@
       </c>
       <c r="D2">
         <f>Pacientes!B4</f>
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E2">
         <f>Calc!H2</f>
-        <v>7.75</v>
+        <v>7.2899999999999991</v>
       </c>
       <c r="G2" t="s">
         <v>7</v>
@@ -4890,7 +4889,7 @@
       </c>
       <c r="B4">
         <f>COUNTIF(Calc!I:I,"Riesgo ALTO")</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4">
         <f>Pacientes!B6</f>
@@ -4948,7 +4947,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -4982,15 +4981,15 @@
       </c>
       <c r="B4">
         <f>Calc!H2</f>
-        <v>7.75</v>
+        <v>7.2899999999999991</v>
       </c>
       <c r="C4" t="str">
         <f>Calc!I2</f>
-        <v>Riesgo Alto</v>
+        <v>Riesgo Bajo-Moderado</v>
       </c>
       <c r="D4" t="str">
         <f>IFERROR(VLOOKUP(C4,Lookups!$A$2:$B$4,2,FALSE),"")</f>
-        <v>Iniciar estatina alta intensidad y seguimiento estrecho</v>
+        <v>Estilo de vida saludable y control periódico</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -5044,7 +5043,7 @@
       </c>
       <c r="D7" t="str">
         <f>IFERROR(VLOOKUP(C7,Lookups!$A$2:$B$4,2,FALSE),"")</f>
-        <v/>
+        <v>Estilo de vida saludable y control periódico</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -5080,7 +5079,7 @@
       </c>
       <c r="D9" s="6" t="str">
         <f>IFERROR(VLOOKUP(C9,Lookups!$A$2:$B$4,2,FALSE),"")</f>
-        <v/>
+        <v>Estilo de vida saludable y control periódico</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -5114,7 +5113,7 @@
   <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="54.85546875" customWidth="1"/>
     <col min="4" max="4" width="9.140625" customWidth="1"/>
   </cols>
@@ -5129,7 +5128,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="B2" t="s">
         <v>13</v>
@@ -5169,7 +5168,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -5179,7 +5178,7 @@
     </row>
     <row r="2" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
@@ -5189,7 +5188,7 @@
     </row>
     <row r="3" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
@@ -5199,7 +5198,7 @@
     </row>
     <row r="4" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -5209,7 +5208,7 @@
     </row>
     <row r="5" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
@@ -5219,7 +5218,7 @@
     </row>
     <row r="6" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -5250,7 +5249,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -5260,7 +5259,7 @@
     </row>
     <row r="2" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B2" s="15"/>
       <c r="C2" s="15"/>
@@ -5270,7 +5269,7 @@
     </row>
     <row r="3" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B3" s="15"/>
       <c r="C3" s="15"/>
@@ -5280,7 +5279,7 @@
     </row>
     <row r="4" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B4" s="15"/>
       <c r="C4" s="15"/>
@@ -5290,7 +5289,7 @@
     </row>
     <row r="5" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B5" s="15"/>
       <c r="C5" s="15"/>
@@ -5300,7 +5299,7 @@
     </row>
     <row r="6" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B6" s="15"/>
       <c r="C6" s="15"/>
